--- a/tests/workbooktests/workbooks/test_ratehelpers.xlsx
+++ b/tests/workbooktests/workbooks/test_ratehelpers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5F18A0-4DE7-4C93-816A-69FC7F3E51BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C52C5C-3CA6-4354-BD71-1BB75877B7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview Tabs" sheetId="18" r:id="rId1"/>
@@ -35,6 +35,20 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -734,8 +748,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -751,9 +765,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -791,7 +805,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -897,7 +911,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1039,7 +1053,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1048,93 +1062,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340204E2-69E6-4DD5-97B8-ED1481D21F17}">
   <dimension ref="A2:A18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.109375" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>187</v>
       </c>
@@ -1147,16 +1161,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65244DF5-80D7-445B-8275-CBDDDF4E3506}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="90.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="77.5703125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="90.6640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="77.5546875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1164,16 +1178,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1184,7 +1198,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1195,7 +1209,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1206,20 +1220,20 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="str">
+        <f>_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360")</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R7C2OvernightIndex,A</v>
+      </c>
+      <c r="C7" s="12" t="str">
+        <f>_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360")</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R7C3OvernightIndex,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1230,7 +1244,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -1238,108 +1252,108 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelper(B4,B5,B6,B7,B8)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelper(C4,C5,C6,C7,C8,C9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="str">
+        <f>_xll.qlOvernightIndexFutureRateHelper(B4,B5,B6,B7,B8)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R10C2OvernightIndexFutureRateHelper,A</v>
+      </c>
+      <c r="C10" s="12" t="str">
+        <f>_xll.qlOvernightIndexFutureRateHelper(C4,C5,C6,C7,C8,C9)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R10C3OvernightIndexFutureRateHelper,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="12">
+        <f>_xll.qlRateHelperQuote(B10)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C11" s="12">
+        <f>_xll.qlRateHelperQuote(C10)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="11">
+        <f>_xll.qlRateHelperLatestDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C12" s="11">
+        <f>_xll.qlRateHelperLatestDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B10)</f>
+        <v>45663</v>
+      </c>
+      <c r="C13" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C10)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C14" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C15" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <f>_xll.qlRateHelperPillarDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C16" s="11">
+        <f>_xll.qlRateHelperPillarDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(C10)</f>
-        <v>#VALUE!</v>
+      <c r="B17" s="12">
+        <f>_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(B10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="12">
+        <f>_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(C10)</f>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -1350,13 +1364,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBCB75F-B7E2-417A-B51A-9EA1B0672E67}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.7109375" customWidth="1"/>
-    <col min="2" max="2" width="70.28515625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="49.6640625" customWidth="1"/>
+    <col min="2" max="2" width="70.33203125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1364,16 +1378,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1381,7 +1395,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>84</v>
       </c>
@@ -1389,7 +1403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -1397,7 +1411,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>86</v>
       </c>
@@ -1405,72 +1419,72 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="12" t="e">
-        <f ca="1">_xll.qlSofrFutureRateHelper(B4,B5,B6,B7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="str">
+        <f>_xll.qlSofrFutureRateHelper(B4,B5,B6,B7)</f>
+        <v>欣[test_ratehelpers.xlsx]SofrFutureRateHelper!R9C2SofrFutureRateHelper,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="12">
+        <f>_xll.qlRateHelperQuote(B9)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="11">
+        <f>_xll.qlRateHelperLatestDate(B9)</f>
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B9)</f>
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B9)</f>
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B9)</f>
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B9)</f>
-        <v>#VALUE!</v>
+      <c r="B15" s="11">
+        <f>_xll.qlRateHelperPillarDate(B9)</f>
+        <v>45778</v>
       </c>
     </row>
   </sheetData>
@@ -1482,14 +1496,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B5DD58-D551-4EB6-8795-9A6336CDACCA}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.5703125" customWidth="1"/>
-    <col min="2" max="2" width="103.42578125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="45.5546875" customWidth="1"/>
+    <col min="2" max="2" width="103.44140625" style="12" customWidth="1"/>
     <col min="3" max="3" width="106" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1497,16 +1511,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -1518,7 +1532,7 @@
       </c>
       <c r="D4" s="12"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1544,7 @@
       </c>
       <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1542,21 +1556,21 @@
       </c>
       <c r="D6" s="12"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
+      <c r="B7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
       </c>
       <c r="D7" s="12"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1568,7 +1582,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1580,7 +1594,7 @@
       </c>
       <c r="D9" s="12"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1592,7 +1606,7 @@
       </c>
       <c r="D10" s="12"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -1604,35 +1618,35 @@
       </c>
       <c r="D11" s="12"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
+      <c r="B12" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R12C2Euribor,A</v>
+      </c>
+      <c r="C12" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R12C3Euribor,A</v>
       </c>
       <c r="D12" s="12"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
+      <c r="B13" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R13C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C13" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R13C3YieldTermStructureHandle,A</v>
       </c>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1644,7 +1658,7 @@
       </c>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -1653,95 +1667,95 @@
       </c>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="12" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencySwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="12" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencySwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="12" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencySwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R16C2ConstNotionalCrossCurrencySwapRateHelper,A</v>
+      </c>
+      <c r="C16" s="12" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencySwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R16C3ConstNotionalCrossCurrencySwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="12">
+        <f>_xll.qlRateHelperQuote(B16)</f>
+        <v>0.04</v>
+      </c>
+      <c r="C17" s="12">
+        <f>_xll.qlRateHelperQuote(C16)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>_xll.qlRateHelperLatestDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C18" s="11">
+        <f>_xll.qlRateHelperLatestDate(C16)</f>
+        <v>45847</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B16)</f>
+        <v>45665</v>
+      </c>
+      <c r="C19" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C16)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C20" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C16)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C21" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C16)</f>
+        <v>45847</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C16)</f>
-        <v>#VALUE!</v>
+      <c r="B22" s="11">
+        <f>_xll.qlRateHelperPillarDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C22" s="11">
+        <f>_xll.qlRateHelperPillarDate(C16)</f>
+        <v>45847</v>
       </c>
     </row>
   </sheetData>
@@ -1753,14 +1767,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE987B6-3AFC-4C21-983D-E8670E499AAD}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="43.6640625" customWidth="1"/>
     <col min="2" max="2" width="105" style="12" customWidth="1"/>
     <col min="3" max="3" width="106" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1768,16 +1782,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -1788,7 +1802,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1799,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1810,20 +1824,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1834,7 +1848,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1845,46 +1859,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R10C2Euribor,A</v>
+      </c>
+      <c r="C10" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R10C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R11C2Euribor,A</v>
+      </c>
+      <c r="C11" s="12" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R11C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -1895,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -1906,7 +1920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1917,7 +1931,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -1925,95 +1939,95 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="12" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="12" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R17C2ConstNotionalCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+      <c r="C17" s="12" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R17C3ConstNotionalCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="12">
+        <f>_xll.qlRateHelperQuote(B17)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C18" s="12">
+        <f>_xll.qlRateHelperQuote(C17)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperLatestDate(B17)</f>
+        <v>45754</v>
+      </c>
+      <c r="C19" s="11">
+        <f>_xll.qlRateHelperLatestDate(C17)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B17)</f>
+        <v>45663</v>
+      </c>
+      <c r="C20" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C17)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B17)</f>
+        <v>45754</v>
+      </c>
+      <c r="C21" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C17)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B17)</f>
+        <v>45754</v>
+      </c>
+      <c r="C22" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C17)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C17)</f>
-        <v>#VALUE!</v>
+      <c r="B23" s="11">
+        <f>_xll.qlRateHelperPillarDate(B17)</f>
+        <v>45754</v>
+      </c>
+      <c r="C23" s="11">
+        <f>_xll.qlRateHelperPillarDate(C17)</f>
+        <v>45755</v>
       </c>
     </row>
   </sheetData>
@@ -2025,14 +2039,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD913001-8432-46A8-B805-3C8877FF8FEE}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.28515625" customWidth="1"/>
-    <col min="2" max="2" width="100.85546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="108.28515625" customWidth="1"/>
+    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="2" max="2" width="100.88671875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="108.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2040,16 +2054,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -2060,7 +2074,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2071,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2082,20 +2096,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -2106,7 +2120,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2117,46 +2131,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlCADLibor("6m")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="12" t="e">
-        <f ca="1">_xll.qlCADLibor("6m")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="str">
+        <f>_xll.qlCADLibor("6m")</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R10C2CADLibor,A</v>
+      </c>
+      <c r="C10" s="12" t="str">
+        <f>_xll.qlCADLibor("6m")</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R10C3CADLibor,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R11C2Euribor,A</v>
+      </c>
+      <c r="C11" s="12" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R11C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>97</v>
       </c>
@@ -2167,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2178,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -2189,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>99</v>
       </c>
@@ -2200,7 +2214,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>100</v>
       </c>
@@ -2208,95 +2222,95 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="12" t="e">
-        <f ca="1">_xll.qlMtMCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15,B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="12" t="e">
-        <f ca="1">_xll.qlMtMCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="str">
+        <f>_xll.qlMtMCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15,B16)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R18C2MtMCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+      <c r="C18" s="12" t="str">
+        <f>_xll.qlMtMCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R18C3MtMCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="12">
+        <f>_xll.qlRateHelperQuote(B18)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C19" s="12">
+        <f>_xll.qlRateHelperQuote(C18)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <f>_xll.qlRateHelperLatestDate(B18)</f>
+        <v>45757</v>
+      </c>
+      <c r="C20" s="11">
+        <f>_xll.qlRateHelperLatestDate(C18)</f>
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B18)</f>
+        <v>45667</v>
+      </c>
+      <c r="C21" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C18)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B18)</f>
+        <v>45757</v>
+      </c>
+      <c r="C22" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C18)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B18)</f>
+        <v>45757</v>
+      </c>
+      <c r="C23" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C18)</f>
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C18)</f>
-        <v>#VALUE!</v>
+      <c r="B24" s="11">
+        <f>_xll.qlRateHelperPillarDate(B18)</f>
+        <v>45757</v>
+      </c>
+      <c r="C24" s="11">
+        <f>_xll.qlRateHelperPillarDate(C18)</f>
+        <v>45758</v>
       </c>
     </row>
   </sheetData>
@@ -2308,13 +2322,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96BD365-E285-4A84-8EB5-437F3B693A20}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.5703125" customWidth="1"/>
-    <col min="2" max="2" width="89.140625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="45.5546875" customWidth="1"/>
+    <col min="2" max="2" width="89.109375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2322,16 +2336,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -2339,7 +2353,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2347,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2355,16 +2369,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -2372,7 +2386,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2380,34 +2394,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R10C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="12" t="e">
-        <f ca="1">_xll.qlAUDLibor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="str">
+        <f>_xll.qlAUDLibor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R11C2AUDLibor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R12C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -2415,76 +2429,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="12" t="e">
-        <f ca="1">_xll.qlIborIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="str">
+        <f>_xll.qlIborIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R14C2IborIborBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="12">
+        <f>_xll.qlRateHelperQuote(B14)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <f>_xll.qlRateHelperLatestDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B14)</f>
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <f>_xll.qlRateHelperPillarDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="12" t="e">
-        <f ca="1">_xll.qlIborIborBasisSwapRateHelperSwap(B14)</f>
-        <v>#VALUE!</v>
+      <c r="B21" s="12" t="str">
+        <f>_xll.qlIborIborBasisSwapRateHelperSwap(B14)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R21C2Swap,A</v>
       </c>
     </row>
   </sheetData>
@@ -2496,13 +2510,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4B8905-8681-4349-B601-E6FC9C6EE563}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.85546875" customWidth="1"/>
+    <col min="1" max="1" width="44.88671875" customWidth="1"/>
     <col min="2" max="2" width="94" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2510,16 +2524,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -2527,7 +2541,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2535,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2543,16 +2557,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="12" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -2560,7 +2574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2568,103 +2582,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R10C2Sofr,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="12" t="e">
-        <f ca="1">_xll.qlAUDLibor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="str">
+        <f>_xll.qlAUDLibor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R11C2AUDLibor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R12C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="str">
+        <f>_xll.qlOvernightIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R13C2OvernightIborBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="12">
+        <f>_xll.qlRateHelperQuote(B13)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="11">
+        <f>_xll.qlRateHelperLatestDate(B13)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B13)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B13)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B13)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperPillarDate(B13)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="12" t="e">
-        <f ca="1">_xll.qlOvernightIborBasisSwapRateHelperSwap(B13)</f>
-        <v>#VALUE!</v>
+      <c r="B20" s="12" t="str">
+        <f>_xll.qlOvernightIborBasisSwapRateHelperSwap(B13)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R20C2Swap,A</v>
       </c>
     </row>
   </sheetData>
@@ -2678,13 +2692,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" customWidth="1"/>
-    <col min="2" max="2" width="82.7109375" customWidth="1"/>
+    <col min="1" max="1" width="42.6640625" customWidth="1"/>
+    <col min="2" max="2" width="82.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2692,16 +2706,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -2709,7 +2723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -2717,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -2725,16 +2739,16 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>60</v>
       </c>
-      <c r="B7" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R7C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -2742,36 +2756,36 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R9C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -2784,14 +2798,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA980392-DB4E-4511-92AD-9631BAA7D1FD}">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
-    <col min="2" max="2" width="73.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="43.6640625" customWidth="1"/>
+    <col min="2" max="2" width="73.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2800,19 +2814,19 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2820,7 +2834,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2828,7 +2842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2836,16 +2850,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2853,7 +2867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2861,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -2869,76 +2883,76 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="12" t="e">
-        <f ca="1">_xll.qlDepositRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="str">
+        <f>_xll.qlDepositRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R11C2DepositRateHelper,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="12">
+        <f>_xll.qlRateHelperQuote(B11)</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="11">
+        <f>_xll.qlRateHelperLatestDate(B11)</f>
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B11)</f>
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B11)</f>
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B11)</f>
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
+        <f>_xll.qlRateHelperPillarDate(B11)</f>
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" s="12"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B19" s="12"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2947,85 +2961,85 @@
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R21C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="12" t="e">
-        <f ca="1">_xll.qlDepositRateHelper2(B20,B21)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="str">
+        <f>_xll.qlDepositRateHelper2(B20,B21)</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R22C2DepositRateHelper,A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="12">
+        <f>_xll.qlRateHelperQuote(B22)</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="11">
+        <f>_xll.qlRateHelperLatestDate(B22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B22)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="11">
+        <f>_xll.qlRateHelperPillarDate(B22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B29" s="12"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B30" s="12"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -3033,7 +3047,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -3041,76 +3055,76 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R33C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="12" t="e">
-        <f ca="1">_xll.qlDepositRateHelper3(B31,B32,B33)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="str">
+        <f>_xll.qlDepositRateHelper3(B31,B32,B33)</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R34C2DepositRateHelper,A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B34)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="12">
+        <f>_xll.qlRateHelperQuote(B34)</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B34)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="11">
+        <f>_xll.qlRateHelperLatestDate(B34)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B34)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B34)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B34)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B34)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B34)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B34)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B34)</f>
-        <v>#VALUE!</v>
+      <c r="B40" s="11">
+        <f>_xll.qlRateHelperPillarDate(B34)</f>
+        <v>45757</v>
       </c>
     </row>
   </sheetData>
@@ -3122,15 +3136,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC39AE1-3C8B-4BAC-BB4F-63180FABE33E}">
   <dimension ref="A1:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="59.7109375" customWidth="1"/>
-    <col min="3" max="3" width="60.140625" customWidth="1"/>
-    <col min="4" max="4" width="52.5703125" customWidth="1"/>
+    <col min="2" max="2" width="59.6640625" customWidth="1"/>
+    <col min="3" max="3" width="60.109375" customWidth="1"/>
+    <col min="4" max="4" width="52.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -3139,21 +3153,21 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3167,7 +3181,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3181,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -3195,7 +3209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3209,24 +3223,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D8" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C8" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3240,7 +3254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -3254,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3268,7 +3282,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -3280,7 +3294,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -3292,7 +3306,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -3304,136 +3318,136 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper(B4,B5,B6,B7,B8,B9,B10,B11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D15" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="str">
+        <f>_xll.qlFRARateHelper(B4,B5,B6,B7,B8,B9,B10,B11,,,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C2FraRateHelper,A</v>
+      </c>
+      <c r="C15" s="12" t="str">
+        <f>_xll.qlFRARateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C3FraRateHelper,A</v>
+      </c>
+      <c r="D15" s="12" t="str">
+        <f>_xll.qlFRARateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D16" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="12">
+        <f>_xll.qlRateHelperQuote(B15)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C16" s="12">
+        <f>_xll.qlRateHelperQuote(C15)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D16" s="12">
+        <f>_xll.qlRateHelperQuote(D15)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
+        <f>_xll.qlRateHelperLatestDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C17" s="11">
+        <f>_xll.qlRateHelperLatestDate(C15)</f>
+        <v>45816</v>
+      </c>
+      <c r="D17" s="11">
+        <f>_xll.qlRateHelperLatestDate(D15)</f>
+        <v>45816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B15)</f>
+        <v>45665</v>
+      </c>
+      <c r="C18" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C15)</f>
+        <v>45663</v>
+      </c>
+      <c r="D18" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D15)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C19" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C15)</f>
+        <v>45845</v>
+      </c>
+      <c r="D19" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D15)</f>
+        <v>45845</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C20" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C15)</f>
+        <v>45845</v>
+      </c>
+      <c r="D20" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D15)</f>
+        <v>45845</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
+        <f>_xll.qlRateHelperPillarDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C21" s="11">
+        <f>_xll.qlRateHelperPillarDate(C15)</f>
+        <v>45816</v>
+      </c>
+      <c r="D21" s="11">
+        <f>_xll.qlRateHelperPillarDate(D15)</f>
+        <v>45816</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
@@ -3447,7 +3461,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -3461,24 +3475,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C26" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D26" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R26C2Euribor,A</v>
+      </c>
+      <c r="C26" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R26C3Euribor,A</v>
+      </c>
+      <c r="D26" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R26C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -3490,7 +3504,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -3500,7 +3514,7 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3512,136 +3526,136 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper2(B24,B25,B26)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C30" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper2(C24,C25,C26,C27,,C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D30" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper2(D24,D25,D26,D27,D28,D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="str">
+        <f>_xll.qlFRARateHelper2(B24,B25,B26)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R30C2FraRateHelper,A</v>
+      </c>
+      <c r="C30" s="12" t="str">
+        <f>_xll.qlFRARateHelper2(C24,C25,C26,C27,,C29)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R30C3FraRateHelper,A</v>
+      </c>
+      <c r="D30" s="12" t="str">
+        <f>_xll.qlFRARateHelper2(D24,D25,D26,D27,D28,D29)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R30C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C31" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D31" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D30)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="12">
+        <f>_xll.qlRateHelperQuote(B30)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C31" s="12">
+        <f>_xll.qlRateHelperQuote(C30)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D31" s="12">
+        <f>_xll.qlRateHelperQuote(D30)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D30)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="11">
+        <f>_xll.qlRateHelperLatestDate(B30)</f>
+        <v>45755</v>
+      </c>
+      <c r="C32" s="11">
+        <f>_xll.qlRateHelperLatestDate(C30)</f>
+        <v>45755</v>
+      </c>
+      <c r="D32" s="11">
+        <f>_xll.qlRateHelperLatestDate(D30)</f>
+        <v>45724</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D30)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B30)</f>
+        <v>45665</v>
+      </c>
+      <c r="C33" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C30)</f>
+        <v>45665</v>
+      </c>
+      <c r="D33" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D30)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D30)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B30)</f>
+        <v>45755</v>
+      </c>
+      <c r="C34" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C30)</f>
+        <v>45755</v>
+      </c>
+      <c r="D34" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D30)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D30)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B30)</f>
+        <v>45755</v>
+      </c>
+      <c r="C35" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C30)</f>
+        <v>45755</v>
+      </c>
+      <c r="D35" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D30)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C36" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C30)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D36" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D30)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="11">
+        <f>_xll.qlRateHelperPillarDate(B30)</f>
+        <v>45755</v>
+      </c>
+      <c r="C36" s="11">
+        <f>_xll.qlRateHelperPillarDate(C30)</f>
+        <v>45755</v>
+      </c>
+      <c r="D36" s="11">
+        <f>_xll.qlRateHelperPillarDate(D30)</f>
+        <v>45724</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>18</v>
       </c>
@@ -3655,7 +3669,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>27</v>
       </c>
@@ -3669,7 +3683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>28</v>
       </c>
@@ -3683,24 +3697,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C42" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D42" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R42C2Euribor,A</v>
+      </c>
+      <c r="C42" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R42C3Euribor,A</v>
+      </c>
+      <c r="D42" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R42C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>37</v>
       </c>
@@ -3712,7 +3726,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>38</v>
       </c>
@@ -3722,7 +3736,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>39</v>
       </c>
@@ -3734,136 +3748,136 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper3(B39,B40,B41,B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C46" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper3(C39,C40,C41,C42,C43,,C45)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D46" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper3(D39,D40,D41,D42,D43,D44,D45)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="12" t="str">
+        <f>_xll.qlFRARateHelper3(B39,B40,B41,B42)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R46C2FraRateHelper,A</v>
+      </c>
+      <c r="C46" s="12" t="str">
+        <f>_xll.qlFRARateHelper3(C39,C40,C41,C42,C43,,C45)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R46C3FraRateHelper,A</v>
+      </c>
+      <c r="D46" s="12" t="str">
+        <f>_xll.qlFRARateHelper3(D39,D40,D41,D42,D43,D44,D45)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R46C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C47" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D47" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="12">
+        <f>_xll.qlRateHelperQuote(B46)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C47" s="12">
+        <f>_xll.qlRateHelperQuote(C46)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D47" s="12">
+        <f>_xll.qlRateHelperQuote(D46)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C48" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D48" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="11">
+        <f>_xll.qlRateHelperLatestDate(B46)</f>
+        <v>45918</v>
+      </c>
+      <c r="C48" s="11">
+        <f>_xll.qlRateHelperLatestDate(C46)</f>
+        <v>45917</v>
+      </c>
+      <c r="D48" s="11">
+        <f>_xll.qlRateHelperLatestDate(D46)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C49" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D49" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B46)</f>
+        <v>45826</v>
+      </c>
+      <c r="C49" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C46)</f>
+        <v>45826</v>
+      </c>
+      <c r="D49" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D46)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C50" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D50" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B46)</f>
+        <v>45917</v>
+      </c>
+      <c r="C50" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C46)</f>
+        <v>45917</v>
+      </c>
+      <c r="D50" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D46)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C51" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D51" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B46)</f>
+        <v>45918</v>
+      </c>
+      <c r="C51" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C46)</f>
+        <v>45918</v>
+      </c>
+      <c r="D51" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D46)</f>
+        <v>45918</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B52" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C52" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C46)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D52" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="11">
+        <f>_xll.qlRateHelperPillarDate(B46)</f>
+        <v>45918</v>
+      </c>
+      <c r="C52" s="11">
+        <f>_xll.qlRateHelperPillarDate(C46)</f>
+        <v>45917</v>
+      </c>
+      <c r="D52" s="11">
+        <f>_xll.qlRateHelperPillarDate(D46)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>18</v>
       </c>
@@ -3877,7 +3891,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>30</v>
       </c>
@@ -3891,24 +3905,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C57" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D57" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R57C2Euribor,A</v>
+      </c>
+      <c r="C57" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R57C3Euribor,A</v>
+      </c>
+      <c r="D57" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R57C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>37</v>
       </c>
@@ -3920,7 +3934,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>38</v>
       </c>
@@ -3930,7 +3944,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
@@ -3942,123 +3956,123 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B61" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper4(B55,B56,B57)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C61" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper4(C55,C56,C57,C58,,C60)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D61" s="12" t="e">
-        <f ca="1">_xll.qlFRARateHelper4(D55,D56,D57,D58,D59,D60)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="12" t="str">
+        <f>_xll.qlFRARateHelper4(B55,B56,B57)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R61C2FraRateHelper,A</v>
+      </c>
+      <c r="C61" s="12" t="str">
+        <f>_xll.qlFRARateHelper4(C55,C56,C57,C58,,C60)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R61C3FraRateHelper,A</v>
+      </c>
+      <c r="D61" s="12" t="str">
+        <f>_xll.qlFRARateHelper4(D55,D56,D57,D58,D59,D60)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R61C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B62" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C62" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D62" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D61)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="12">
+        <f>_xll.qlRateHelperQuote(B61)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C62" s="12">
+        <f>_xll.qlRateHelperQuote(C61)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D62" s="12">
+        <f>_xll.qlRateHelperQuote(D61)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C63" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D63" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D61)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="11">
+        <f>_xll.qlRateHelperLatestDate(B61)</f>
+        <v>45938</v>
+      </c>
+      <c r="C63" s="11">
+        <f>_xll.qlRateHelperLatestDate(C61)</f>
+        <v>45938</v>
+      </c>
+      <c r="D63" s="11">
+        <f>_xll.qlRateHelperLatestDate(D61)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C64" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D64" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D61)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B61)</f>
+        <v>45846</v>
+      </c>
+      <c r="C64" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C61)</f>
+        <v>45846</v>
+      </c>
+      <c r="D64" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D61)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C65" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D65" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D61)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B61)</f>
+        <v>45938</v>
+      </c>
+      <c r="C65" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C61)</f>
+        <v>45938</v>
+      </c>
+      <c r="D65" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D61)</f>
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C66" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D66" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D61)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B61)</f>
+        <v>45938</v>
+      </c>
+      <c r="C66" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C61)</f>
+        <v>45938</v>
+      </c>
+      <c r="D66" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D61)</f>
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C67" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D67" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D61)</f>
-        <v>#VALUE!</v>
+      <c r="B67" s="11">
+        <f>_xll.qlRateHelperPillarDate(B61)</f>
+        <v>45938</v>
+      </c>
+      <c r="C67" s="11">
+        <f>_xll.qlRateHelperPillarDate(C61)</f>
+        <v>45938</v>
+      </c>
+      <c r="D67" s="11">
+        <f>_xll.qlRateHelperPillarDate(D61)</f>
+        <v>45846</v>
       </c>
     </row>
   </sheetData>
@@ -4070,14 +4084,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AFCFAD-5375-4B86-AD50-9C25C7C81EAE}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.85546875" customWidth="1"/>
-    <col min="2" max="2" width="104.5703125" customWidth="1"/>
+    <col min="1" max="1" width="45.88671875" customWidth="1"/>
+    <col min="2" max="2" width="104.5546875" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -4086,20 +4100,20 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -4110,7 +4124,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -4121,7 +4135,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -4132,20 +4146,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>119</v>
       </c>
@@ -4156,7 +4170,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>120</v>
       </c>
@@ -4167,7 +4181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>121</v>
       </c>
@@ -4178,7 +4192,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -4187,7 +4201,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -4196,117 +4210,117 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper(C4,C5,C6,C7,C8,C9,C10,,C12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="str">
+        <f>_xll.qlFuturesRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R13C2FuturesRateHelper,A</v>
+      </c>
+      <c r="C13" s="12" t="str">
+        <f>_xll.qlFuturesRateHelper(C4,C5,C6,C7,C8,C9,C10,,C12)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R13C3FuturesRateHelper,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="12">
+        <f>_xll.qlRateHelperQuote(B13)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C14" s="12">
+        <f>_xll.qlRateHelperQuote(C13)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="11">
+        <f>_xll.qlRateHelperLatestDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C15" s="11">
+        <f>_xll.qlRateHelperLatestDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B13)</f>
+        <v>45826</v>
+      </c>
+      <c r="C16" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C13)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C17" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C18" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperPillarDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C19" s="11">
+        <f>_xll.qlRateHelperPillarDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12">
+        <f>_xll.qlFuturesRateConvexityAdjustment(B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="12">
+        <f>_xll.qlFuturesRateConvexityAdjustment(C13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>116</v>
       </c>
@@ -4317,7 +4331,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>117</v>
       </c>
@@ -4328,7 +4342,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -4339,7 +4353,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -4350,7 +4364,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -4359,7 +4373,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -4368,111 +4382,111 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper2(B23,B24,B25,B26)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C29" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper2(C23,C24,C25,C26,,C28)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" t="str">
+        <f>_xll.qlFuturesRateHelper2(B23,B24,B25,B26)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R29C2FuturesRateHelper,A</v>
+      </c>
+      <c r="C29" t="str">
+        <f>_xll.qlFuturesRateHelper2(C23,C24,C25,C26,,C28)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R29C3FuturesRateHelper,A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C30" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="12">
+        <f>_xll.qlRateHelperQuote(B29)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C30" s="12">
+        <f>_xll.qlRateHelperQuote(C29)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C31" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="11">
+        <f>_xll.qlRateHelperLatestDate(B29)</f>
+        <v>45917</v>
+      </c>
+      <c r="C31" s="11">
+        <f>_xll.qlRateHelperLatestDate(C29)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B29)</f>
+        <v>45826</v>
+      </c>
+      <c r="C32" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C29)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B29)</f>
+        <v>45917</v>
+      </c>
+      <c r="C33" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C29)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B29)</f>
+        <v>45917</v>
+      </c>
+      <c r="C34" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C29)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="11">
+        <f>_xll.qlRateHelperPillarDate(B29)</f>
+        <v>45917</v>
+      </c>
+      <c r="C35" s="11">
+        <f>_xll.qlRateHelperPillarDate(C29)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C36" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="12">
+        <f>_xll.qlFuturesRateConvexityAdjustment(B29)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="12">
+        <f>_xll.qlFuturesRateConvexityAdjustment(C29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>116</v>
       </c>
@@ -4483,7 +4497,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>117</v>
       </c>
@@ -4494,20 +4508,20 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C41" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R41C2Euribor,A</v>
+      </c>
+      <c r="C41" s="12" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R41C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -4516,7 +4530,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -4525,108 +4539,108 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper3(B39,B40,B41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C44" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper3(C39,C40,C41,,C43)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" t="str">
+        <f>_xll.qlFuturesRateHelper3(B39,B40,B41)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R44C2FuturesRateHelper,A</v>
+      </c>
+      <c r="C44" t="str">
+        <f>_xll.qlFuturesRateHelper3(C39,C40,C41,,C43)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R44C3FuturesRateHelper,A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C45" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="12">
+        <f>_xll.qlRateHelperQuote(B44)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C45" s="12">
+        <f>_xll.qlRateHelperQuote(C44)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C46" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="11">
+        <f>_xll.qlRateHelperLatestDate(B44)</f>
+        <v>46009</v>
+      </c>
+      <c r="C46" s="11">
+        <f>_xll.qlRateHelperLatestDate(C44)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C47" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B44)</f>
+        <v>45826</v>
+      </c>
+      <c r="C47" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C44)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C48" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B44)</f>
+        <v>46009</v>
+      </c>
+      <c r="C48" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C44)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C49" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B44)</f>
+        <v>46009</v>
+      </c>
+      <c r="C49" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C44)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C50" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="11">
+        <f>_xll.qlRateHelperPillarDate(B44)</f>
+        <v>46009</v>
+      </c>
+      <c r="C50" s="11">
+        <f>_xll.qlRateHelperPillarDate(C44)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C51" s="12" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(C44)</f>
-        <v>#VALUE!</v>
+      <c r="B51" s="12">
+        <f>_xll.qlFuturesRateConvexityAdjustment(B44)</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="12">
+        <f>_xll.qlFuturesRateConvexityAdjustment(C44)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4637,14 +4651,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F658185D-C335-4A5F-955B-EF5C79D6BAD3}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.140625" customWidth="1"/>
-    <col min="2" max="2" width="65.140625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="45.109375" customWidth="1"/>
+    <col min="2" max="2" width="65.109375" style="12" customWidth="1"/>
     <col min="3" max="4" width="71" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -4652,23 +4666,23 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -4684,7 +4698,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -4700,26 +4714,26 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C6" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D6" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
+      <c r="B6" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C6" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D6" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -4735,7 +4749,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>128</v>
       </c>
@@ -4751,7 +4765,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -4767,26 +4781,26 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D10" s="12" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
+      <c r="B10" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R10C2Euribor,A</v>
+      </c>
+      <c r="C10" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R10C3Euribor,A</v>
+      </c>
+      <c r="D10" s="12" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R10C4Euribor,A</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -4800,7 +4814,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>130</v>
       </c>
@@ -4814,23 +4828,23 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>153</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="11" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D13" s="11" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
+      <c r="C13" s="11" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R13C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D13" s="11" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R13C4YieldTermStructureHandle,A</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -4844,7 +4858,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -4858,7 +4872,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -4870,7 +4884,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -4884,7 +4898,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -4898,166 +4912,166 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,,C17,C18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D19" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="str">
+        <f>_xll.qlSwapRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R19C2SwapRateHelper,A</v>
+      </c>
+      <c r="C19" s="12" t="str">
+        <f>_xll.qlSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,,C17,C18)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R19C3SwapRateHelper,A</v>
+      </c>
+      <c r="D19" s="12" t="str">
+        <f>_xll.qlSwapRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R19C4SwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D20" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="12">
+        <f>_xll.qlRateHelperQuote(B19)</f>
+        <v>0.04</v>
+      </c>
+      <c r="C20" s="12">
+        <f>_xll.qlRateHelperQuote(C19)</f>
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="12">
+        <f>_xll.qlRateHelperQuote(D19)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D21" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
+        <f>_xll.qlRateHelperLatestDate(B19)</f>
+        <v>45755</v>
+      </c>
+      <c r="C21" s="11">
+        <f>_xll.qlRateHelperLatestDate(C19)</f>
+        <v>45846</v>
+      </c>
+      <c r="D21" s="11">
+        <f>_xll.qlRateHelperLatestDate(D19)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D22" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B19)</f>
+        <v>45665</v>
+      </c>
+      <c r="C22" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C19)</f>
+        <v>45755</v>
+      </c>
+      <c r="D22" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D19)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D23" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B19)</f>
+        <v>45755</v>
+      </c>
+      <c r="C23" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C19)</f>
+        <v>45846</v>
+      </c>
+      <c r="D23" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D19)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D24" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B19)</f>
+        <v>45755</v>
+      </c>
+      <c r="C24" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C19)</f>
+        <v>45846</v>
+      </c>
+      <c r="D24" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D19)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C25" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D25" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="11">
+        <f>_xll.qlRateHelperPillarDate(B19)</f>
+        <v>45755</v>
+      </c>
+      <c r="C25" s="11">
+        <f>_xll.qlRateHelperPillarDate(C19)</f>
+        <v>45846</v>
+      </c>
+      <c r="D25" s="11">
+        <f>_xll.qlRateHelperPillarDate(D19)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C26" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D26" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="12">
+        <f>_xll.qlSwapRateHelperSpread(B19)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="12">
+        <f>_xll.qlSwapRateHelperSpread(C19)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="12">
+        <f>_xll.qlSwapRateHelperSpread(D19)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C27" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D27" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(D19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="str">
+        <f>_xll.qlSwapRateHelperSwap(B19)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R27C2VanillaSwap,A</v>
+      </c>
+      <c r="C27" s="12" t="str">
+        <f>_xll.qlSwapRateHelperSwap(C19)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R27C3VanillaSwap,A</v>
+      </c>
+      <c r="D27" s="12" t="str">
+        <f>_xll.qlSwapRateHelperSwap(D19)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R27C4VanillaSwap,A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>55</v>
       </c>
@@ -5071,7 +5085,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>0</v>
       </c>
@@ -5085,7 +5099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>47</v>
       </c>
@@ -5099,7 +5113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>56</v>
       </c>
@@ -5113,24 +5127,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="14" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C34" s="14" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D34" s="14" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="14" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C34" s="14" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D34" s="14" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>57</v>
       </c>
@@ -5144,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>58</v>
       </c>
@@ -5158,7 +5172,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>59</v>
       </c>
@@ -5172,41 +5186,41 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="14" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C38" s="14" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D38" s="14" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="14" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C2Euribor,A</v>
+      </c>
+      <c r="C38" s="14" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C3Euribor,A</v>
+      </c>
+      <c r="D38" s="14" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="14" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C39" s="14" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D39" s="14" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="14" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C39" s="14" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D39" s="14" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C4YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>125</v>
       </c>
@@ -5220,24 +5234,24 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B41" s="12" t="e">
-        <f ca="1">_xll.qlSwapIndex(B30,B31,B32,B33,B34,B35,B36,B37,B38,B39)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C41" s="12" t="e">
-        <f ca="1">_xll.qlSwapIndex(C30,C31,C32,C33,C34,C35,C36,C37,C38,C39)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D41" s="12" t="e">
-        <f ca="1">_xll.qlSwapIndex(D30,D31,D32,D33,D34,D35,D36,D37,D38,D39)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="str">
+        <f>_xll.qlSwapIndex(B30,B31,B32,B33,B34,B35,B36,B37,B38,B39)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C2SwapIndex,A</v>
+      </c>
+      <c r="C41" s="12" t="str">
+        <f>_xll.qlSwapIndex(C30,C31,C32,C33,C34,C35,C36,C37,C38,C39)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C3SwapIndex,A</v>
+      </c>
+      <c r="D41" s="12" t="str">
+        <f>_xll.qlSwapIndex(D30,D31,D32,D33,D34,D35,D36,D37,D38,D39)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C4SwapIndex,A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
@@ -5248,7 +5262,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>130</v>
       </c>
@@ -5259,20 +5273,20 @@
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D44" s="12" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C44" s="12" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R44C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D44" s="12" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R44C4YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>134</v>
       </c>
@@ -5283,7 +5297,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>135</v>
       </c>
@@ -5291,7 +5305,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>120</v>
       </c>
@@ -5302,7 +5316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
@@ -5313,163 +5327,163 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelper2(B40,B41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C49" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelper2(C40,C41,C42,C43,C44,C45,,C47,C48)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D49" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelper2(D40,D41,D42,D43,D44,D45,D46,D47,D48)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="12" t="str">
+        <f>_xll.qlSwapRateHelper2(B40,B41)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C2SwapRateHelper,A</v>
+      </c>
+      <c r="C49" s="12" t="str">
+        <f>_xll.qlSwapRateHelper2(C40,C41,C42,C43,C44,C45,,C47,C48)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C3SwapRateHelper,A</v>
+      </c>
+      <c r="D49" s="12" t="str">
+        <f>_xll.qlSwapRateHelper2(D40,D41,D42,D43,D44,D45,D46,D47,D48)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C4SwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B50" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C50" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D50" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="12">
+        <f>_xll.qlRateHelperQuote(B49)</f>
+        <v>0.04</v>
+      </c>
+      <c r="C50" s="12">
+        <f>_xll.qlRateHelperQuote(C49)</f>
+        <v>0.04</v>
+      </c>
+      <c r="D50" s="12">
+        <f>_xll.qlRateHelperQuote(D49)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C51" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D51" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="11">
+        <f>_xll.qlRateHelperLatestDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C51" s="11">
+        <f>_xll.qlRateHelperLatestDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D51" s="11">
+        <f>_xll.qlRateHelperLatestDate(D49)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C52" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D52" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B49)</f>
+        <v>45665</v>
+      </c>
+      <c r="C52" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C49)</f>
+        <v>45698</v>
+      </c>
+      <c r="D52" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D49)</f>
+        <v>45698</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C53" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D53" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C53" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D53" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D49)</f>
+        <v>45789</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B54" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C54" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D54" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C54" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D54" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D49)</f>
+        <v>45789</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C55" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D55" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="11">
+        <f>_xll.qlRateHelperPillarDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C55" s="11">
+        <f>_xll.qlRateHelperPillarDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D55" s="11">
+        <f>_xll.qlRateHelperPillarDate(D49)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C56" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D56" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="12">
+        <f>_xll.qlSwapRateHelperSpread(B49)</f>
+        <v>0</v>
+      </c>
+      <c r="C56" s="12">
+        <f>_xll.qlSwapRateHelperSpread(C49)</f>
+        <v>0.6</v>
+      </c>
+      <c r="D56" s="12">
+        <f>_xll.qlSwapRateHelperSpread(D49)</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B57" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(B49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C57" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(C49)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D57" s="12" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(D49)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="12" t="str">
+        <f>_xll.qlSwapRateHelperSwap(B49)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C2VanillaSwap,A</v>
+      </c>
+      <c r="C57" s="12" t="str">
+        <f>_xll.qlSwapRateHelperSwap(C49)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C3VanillaSwap,A</v>
+      </c>
+      <c r="D57" s="12" t="str">
+        <f>_xll.qlSwapRateHelperSwap(D49)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C4VanillaSwap,A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B63" s="11"/>
     </row>
   </sheetData>
@@ -5484,7 +5498,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5496,33 +5510,33 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A2:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I7" s="1"/>
     </row>
   </sheetData>
@@ -5533,14 +5547,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8D3E72-38D5-454D-A3CB-8D63AEF54296}">
   <dimension ref="A1:D36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.42578125" customWidth="1"/>
-    <col min="2" max="2" width="66.85546875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="66.88671875" style="12" customWidth="1"/>
     <col min="3" max="4" width="76" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5548,19 +5562,19 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>140</v>
       </c>
@@ -5574,7 +5588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -5588,7 +5602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -5602,38 +5616,38 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="11" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="11" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D7" s="11" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C2Sofr,A</v>
+      </c>
+      <c r="C7" s="11" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C3Sofr,A</v>
+      </c>
+      <c r="D7" s="11" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C4Sofr,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>153</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="11" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D8" s="11" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="11" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R8C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R8C4YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -5645,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -5657,7 +5671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -5669,7 +5683,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -5681,21 +5695,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>154</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D13" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D13" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -5707,7 +5721,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>146</v>
       </c>
@@ -5719,7 +5733,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>134</v>
       </c>
@@ -5731,7 +5745,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -5741,7 +5755,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>147</v>
       </c>
@@ -5753,7 +5767,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
@@ -5765,7 +5779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -5777,21 +5791,21 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>156</v>
       </c>
       <c r="B21" s="11"/>
-      <c r="C21" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D21" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D21" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>148</v>
       </c>
@@ -5803,7 +5817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>149</v>
       </c>
@@ -5815,7 +5829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -5827,7 +5841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -5835,7 +5849,7 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -5847,21 +5861,21 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>158</v>
       </c>
       <c r="B27" s="11"/>
-      <c r="C27" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D27" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D27" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -5873,140 +5887,140 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="12" t="e">
-        <f ca="1">_xll.qlOISRateHelper(B4,B5,B6,B7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C29" s="12" t="e">
-        <f ca="1">_xll.qlOISRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,,C18,C19,C20,C21,C22,C23,C24,,C26,C27,C28)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D29" s="12" t="e">
-        <f ca="1">_xll.qlOISRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D23,D24,,D26,D27,D28)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="str">
+        <f>_xll.qlOISRateHelper(B4,B5,B6,B7)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C2OISRateHelper,A</v>
+      </c>
+      <c r="C29" s="12" t="str">
+        <f>_xll.qlOISRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,,C18,C19,C20,C21,C22,C23,C24,,C26,C27,C28)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C3OISRateHelper,A</v>
+      </c>
+      <c r="D29" s="12" t="str">
+        <f>_xll.qlOISRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D23,D24,,D26,D27,D28)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C4OISRateHelper,A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C30" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D30" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="12">
+        <f>_xll.qlRateHelperQuote(B29)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C30" s="12">
+        <f>_xll.qlRateHelperQuote(C29)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D30" s="12">
+        <f>_xll.qlRateHelperQuote(D29)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C31" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D31" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="11">
+        <f>_xll.qlRateHelperLatestDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C31" s="11">
+        <f>_xll.qlRateHelperLatestDate(C29)</f>
+        <v>45791</v>
+      </c>
+      <c r="D31" s="11">
+        <f>_xll.qlRateHelperLatestDate(D29)</f>
+        <v>45791</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D32" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B29)</f>
+        <v>45666</v>
+      </c>
+      <c r="C32" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C29)</f>
+        <v>45698</v>
+      </c>
+      <c r="D32" s="11">
+        <f>_xll.qlRateHelperEarliestDate(D29)</f>
+        <v>45698</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D33" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C33" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C29)</f>
+        <v>45789</v>
+      </c>
+      <c r="D33" s="11">
+        <f>_xll.qlRateHelperMaturityDate(D29)</f>
+        <v>45789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D34" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C34" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C29)</f>
+        <v>45791</v>
+      </c>
+      <c r="D34" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(D29)</f>
+        <v>45791</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D35" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="11">
+        <f>_xll.qlRateHelperPillarDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C35" s="11">
+        <f>_xll.qlRateHelperPillarDate(C29)</f>
+        <v>45789</v>
+      </c>
+      <c r="D35" s="11">
+        <f>_xll.qlRateHelperPillarDate(D29)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="12" t="e">
-        <f ca="1">_xll.qlOISRateHelperSwap(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C36" s="12" t="e">
-        <f ca="1">_xll.qlOISRateHelperSwap(C29)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D36" s="12" t="e">
-        <f ca="1">_xll.qlOISRateHelperSwap(D29)</f>
-        <v>#VALUE!</v>
+      <c r="B36" s="12" t="str">
+        <f>_xll.qlOISRateHelperSwap(B29)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R36C2OvernightIndexedSwap,A</v>
+      </c>
+      <c r="C36" s="12" t="str">
+        <f>_xll.qlOISRateHelperSwap(C29)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R36C3OvernightIndexedSwap,A</v>
+      </c>
+      <c r="D36" s="12" t="str">
+        <f>_xll.qlOISRateHelperSwap(D29)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R36C4OvernightIndexedSwap,A</v>
       </c>
     </row>
   </sheetData>
@@ -6018,14 +6032,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C2BEAF-FCDE-48B0-B97E-27F830DD2C98}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" customWidth="1"/>
-    <col min="2" max="2" width="69.140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" customWidth="1"/>
+    <col min="2" max="2" width="69.109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="73.33203125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -6033,19 +6047,19 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="11" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -6056,7 +6070,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -6067,7 +6081,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -6078,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -6089,20 +6103,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C8" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -6113,7 +6127,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -6124,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -6135,235 +6149,235 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="11" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="11" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="11" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>161</v>
       </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="11" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="11" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R14C2FxSwapRateHelper,A</v>
+      </c>
+      <c r="C14" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13)</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R14C3FxSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="12" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="12">
+        <f>_xll.qlRateHelperQuote(B14)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C15" s="12">
+        <f>_xll.qlRateHelperQuote(C14)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <f>_xll.qlRateHelperLatestDate(B14)</f>
+        <v>46324</v>
+      </c>
+      <c r="C16" s="11">
+        <f>_xll.qlRateHelperLatestDate(C14)</f>
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
+        <f>_xll.qlRateHelperEarliestDate(B14)</f>
+        <v>46232</v>
+      </c>
+      <c r="C17" s="11">
+        <f>_xll.qlRateHelperEarliestDate(C14)</f>
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>_xll.qlRateHelperMaturityDate(B14)</f>
+        <v>46324</v>
+      </c>
+      <c r="C18" s="11">
+        <f>_xll.qlRateHelperMaturityDate(C14)</f>
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(B14)</f>
+        <v>46324</v>
+      </c>
+      <c r="C19" s="11">
+        <f>_xll.qlRateHelperLatestRelevantDate(C14)</f>
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="11" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <f>_xll.qlRateHelperPillarDate(B14)</f>
+        <v>46324</v>
+      </c>
+      <c r="C20" s="11">
+        <f>_xll.qlRateHelperPillarDate(C14)</f>
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperSpot(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperSpot(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12">
+        <f>_xll.qlFxSwapRateHelperSpot(B14)</f>
+        <v>0.97</v>
+      </c>
+      <c r="C21" s="12">
+        <f>_xll.qlFxSwapRateHelperSpot(C14)</f>
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTenor(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTenor(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperTenor(B14)</f>
+        <v>3M</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperTenor(C14)</f>
+        <v>3M</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperFixingDays(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperFixingDays(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="12">
+        <f>_xll.qlFxSwapRateHelperFixingDays(B14)</f>
+        <v>2</v>
+      </c>
+      <c r="C23" s="12">
+        <f>_xll.qlFxSwapRateHelperFixingDays(C14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperCalendar(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperCalendar(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperCalendar(B14)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C24" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperCalendar(C14)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="16" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperBusinessDayConvention(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C25" s="16" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperBusinessDayConvention(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="16">
+        <f>_xll.qlFxSwapRateHelperBusinessDayConvention(B14)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="16">
+        <f>_xll.qlFxSwapRateHelperBusinessDayConvention(C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperEndOfMonth(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C26" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperEndOfMonth(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="b">
+        <f>_xll.qlFxSwapRateHelperEndOfMonth(B14)</f>
+        <v>1</v>
+      </c>
+      <c r="C26" s="12" t="b">
+        <f>_xll.qlFxSwapRateHelperEndOfMonth(C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C27" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="b">
+        <f>_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(B14)</f>
+        <v>1</v>
+      </c>
+      <c r="C27" s="12" t="b">
+        <f>_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTradingCalendar(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C28" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTradingCalendar(C14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperTradingCalendar(B14)</f>
+        <v>Null</v>
+      </c>
+      <c r="C28" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperTradingCalendar(C14)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperAdjustmentCalendar(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C29" s="12" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperAdjustmentCalendar(C14)</f>
-        <v>#VALUE!</v>
+      <c r="B29" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperAdjustmentCalendar(B14)</f>
+        <v>JoinHolidays(Null, TARGET)</v>
+      </c>
+      <c r="C29" s="12" t="str">
+        <f>_xll.qlFxSwapRateHelperAdjustmentCalendar(C14)</f>
+        <v>JoinHolidays(TARGET, TARGET)</v>
       </c>
     </row>
   </sheetData>
